--- a/data/export/2026-10-27-operations.xlsx
+++ b/data/export/2026-10-27-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,17 +704,17 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -720,13 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -908,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +963,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -958,7 +974,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -991,32 +1007,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,17 +1068,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1068,13 +1088,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1164,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1190,7 +1214,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1459,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1507,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1526,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1562,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1623,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1642,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1855,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1910,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1971,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1990,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2002,35 +2026,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2087,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2106,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2131,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2207,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2226,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2223,7 +2251,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2234,7 +2262,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2247,22 +2275,22 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2300,7 +2328,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2342,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2350,7 +2378,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2391,7 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2373,7 +2401,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2411,12 +2439,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2458,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,35 +2494,35 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2532,7 +2560,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2574,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2610,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2648,7 +2676,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2690,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2726,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2792,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2806,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2842,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2903,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2922,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2958,3487 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-operations.xlsx
+++ b/data/export/2026-10-27-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,14 +719,14 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -891,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -924,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -948,17 +952,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -968,13 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1017,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1044,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1083,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1131,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1164,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1188,33 +1200,37 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1319,7 +1335,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1330,7 +1346,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1379,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1440,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1551,7 +1575,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1562,7 +1586,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1678,7 +1702,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1768,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1783,7 +1807,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1794,7 +1818,7 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1884,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1910,7 +1934,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2000,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2026,7 +2050,7 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2116,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2146,7 +2170,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2159,22 +2183,22 @@
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2212,7 +2236,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2226,7 +2250,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2256,41 +2280,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2323,12 +2351,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2342,7 +2370,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2367,46 +2395,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2439,12 +2471,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2458,7 +2490,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2483,46 +2515,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2555,12 +2591,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2574,7 +2610,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2610,35 +2646,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2671,12 +2707,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2690,7 +2726,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2715,46 +2751,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2787,12 +2827,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2806,7 +2846,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2831,7 +2871,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2842,35 +2882,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2903,12 +2943,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2922,7 +2962,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2947,46 +2987,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3019,12 +3063,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3038,7 +3082,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3063,7 +3107,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3074,35 +3118,35 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3135,12 +3179,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3154,7 +3198,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3179,7 +3223,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3190,7 +3234,7 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3247,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3213,7 +3257,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3223,40 +3267,44 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3270,7 +3318,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3280,33 +3328,37 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3319,60 +3371,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3386,7 +3442,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3396,33 +3452,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3435,60 +3495,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3502,7 +3566,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3512,17 +3576,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3532,13 +3596,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3619,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3561,7 +3629,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3599,12 +3667,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3618,7 +3686,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3654,7 +3722,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3667,32 +3735,32 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq39，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3715,12 +3783,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3728,13 +3796,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr"/>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3770,7 +3854,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3867,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3793,7 +3877,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3831,12 +3915,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3850,7 +3934,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3886,7 +3970,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3983,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3909,7 +3993,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3947,12 +4031,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3966,7 +4050,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4002,7 +4086,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4099,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4025,7 +4109,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4063,12 +4147,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4082,7 +4166,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4118,7 +4202,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4215,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4141,7 +4225,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4179,12 +4263,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4198,7 +4282,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4234,7 +4318,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4247,22 +4331,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4295,12 +4379,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4314,7 +4398,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4350,7 +4434,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4363,22 +4447,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4411,12 +4495,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4430,7 +4514,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4466,7 +4550,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4479,22 +4563,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4527,12 +4611,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4546,7 +4630,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4582,35 +4666,35 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4643,12 +4727,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4662,7 +4746,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4687,7 +4771,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4698,35 +4782,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4759,12 +4843,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4778,7 +4862,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4814,35 +4898,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4875,12 +4959,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4894,7 +4978,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4930,35 +5014,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4991,12 +5075,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5010,7 +5094,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5046,35 +5130,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5107,12 +5191,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5126,7 +5210,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5162,35 +5246,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5223,12 +5307,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5242,7 +5326,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5278,35 +5362,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5339,12 +5423,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5358,7 +5442,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5394,35 +5478,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5455,12 +5539,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5474,7 +5558,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5510,35 +5594,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5571,12 +5655,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5590,7 +5674,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5626,35 +5710,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5687,12 +5771,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5706,7 +5790,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5742,35 +5826,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5803,12 +5887,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5822,7 +5906,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5858,35 +5942,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5919,12 +6003,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5938,7 +6022,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5974,35 +6058,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6040,7 +6124,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6054,7 +6138,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6090,35 +6174,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6151,12 +6235,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6170,7 +6254,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6206,35 +6290,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6267,12 +6351,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6286,7 +6370,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6322,35 +6406,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6388,7 +6472,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6402,7 +6486,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6432,13 +6516,3177 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC51" s="2" t="inlineStr"/>
-      <c r="AD51" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-operations.xlsx
+++ b/data/export/2026-10-27-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD78"/>
+  <dimension ref="A1:AD100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1503,32 +1503,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1536,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1560,17 +1564,17 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1580,13 +1584,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1619,32 +1627,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1652,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1676,33 +1688,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1851,32 +1867,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -1884,7 +1904,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1908,33 +1928,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1967,32 +1991,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2000,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2024,33 +2052,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2155,7 +2187,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2236,7 +2268,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2323,32 +2355,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2356,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2380,37 +2416,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2512,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2596,7 +2632,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2712,7 +2748,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2766,7 +2802,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2868,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2948,7 +2984,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3002,7 +3038,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3104,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3112,13 +3148,17 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3131,22 +3171,22 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3184,7 +3224,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3228,83 +3268,83 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3318,7 +3358,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3328,17 +3368,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3348,87 +3388,79 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>136.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3442,7 +3474,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3452,17 +3484,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3477,82 +3509,78 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3566,7 +3594,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3576,65 +3604,65 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3667,12 +3695,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3686,7 +3714,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3711,56 +3739,60 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq39，推进11站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3783,12 +3815,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3796,29 +3828,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>物理seq30（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>07:53</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3843,18 +3859,22 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3887,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3877,7 +3897,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3887,40 +3907,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3934,7 +3958,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3944,33 +3968,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3983,7 +4011,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3993,7 +4021,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4003,32 +4031,36 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4036,7 +4068,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4050,7 +4082,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4060,33 +4092,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4099,60 +4135,64 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4166,7 +4206,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4176,33 +4216,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4215,60 +4259,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4282,7 +4330,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4292,33 +4340,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4383,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4341,7 +4393,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4351,12 +4403,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4379,12 +4431,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4392,13 +4444,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4423,7 +4491,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4447,22 +4515,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4495,12 +4563,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4514,7 +4582,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4539,7 +4607,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4563,7 +4631,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4573,7 +4641,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4583,40 +4651,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4630,7 +4702,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4640,33 +4712,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4755,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4689,7 +4765,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4699,40 +4775,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4746,7 +4826,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4756,33 +4836,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4879,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4805,7 +4889,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4815,40 +4899,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4862,7 +4950,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4872,33 +4960,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4911,22 +5003,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4959,12 +5051,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4978,7 +5070,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5003,7 +5095,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5027,7 +5119,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5037,7 +5129,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5075,12 +5167,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5094,7 +5186,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5143,32 +5235,32 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:37</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -5191,12 +5283,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5204,13 +5296,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5259,7 +5367,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5269,7 +5377,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5307,12 +5415,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5326,7 +5434,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5375,7 +5483,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5385,7 +5493,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5423,12 +5531,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5442,7 +5550,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5491,7 +5599,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5501,7 +5609,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5511,12 +5619,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5539,12 +5647,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5552,13 +5660,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5607,7 +5731,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5617,7 +5741,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5655,12 +5779,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5674,7 +5798,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5723,7 +5847,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5733,7 +5857,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5776,7 +5900,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5790,7 +5914,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5839,7 +5963,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5849,7 +5973,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5887,12 +6011,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5906,7 +6030,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5955,7 +6079,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5965,7 +6089,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6003,12 +6127,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6022,7 +6146,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6071,7 +6195,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6081,7 +6205,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6119,12 +6243,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6138,7 +6262,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6187,22 +6311,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6240,7 +6364,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6254,7 +6378,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6303,22 +6427,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6351,12 +6475,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6370,7 +6494,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6419,22 +6543,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6467,12 +6591,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6486,7 +6610,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6511,22 +6635,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>153.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6539,22 +6659,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6592,7 +6712,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6606,7 +6726,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6631,84 +6751,76 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>136.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6716,7 +6828,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6730,7 +6842,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6740,65 +6852,61 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6836,7 +6944,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6850,7 +6958,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6875,7 +6983,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6886,35 +6994,35 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6947,12 +7055,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6966,7 +7074,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6991,7 +7099,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7002,77 +7110,73 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7086,7 +7190,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7096,17 +7200,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7121,40 +7225,40 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7187,12 +7291,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7206,7 +7310,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7236,41 +7340,45 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7303,12 +7411,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7322,7 +7430,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7352,41 +7460,45 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7419,12 +7531,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7438,7 +7550,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7468,41 +7580,45 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7535,12 +7651,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7554,7 +7670,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7579,7 +7695,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7590,35 +7706,35 @@
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7651,12 +7767,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7670,7 +7786,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7695,7 +7811,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7706,35 +7822,35 @@
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7767,12 +7883,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7786,7 +7902,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7816,41 +7932,45 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7883,12 +8003,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7902,7 +8022,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7927,46 +8047,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7999,12 +8123,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8018,7 +8142,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8043,46 +8167,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8115,12 +8243,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8134,7 +8262,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8159,7 +8287,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8170,7 +8298,7 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8311,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8193,50 +8321,54 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
           <t>07:42</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8250,7 +8382,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8260,33 +8392,37 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8299,22 +8435,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8352,7 +8488,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8366,7 +8502,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8391,7 +8527,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8415,7 +8551,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8425,7 +8561,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8463,12 +8599,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8482,7 +8618,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8507,7 +8643,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8531,7 +8667,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8541,7 +8677,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8551,40 +8687,44 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8598,7 +8738,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8608,17 +8748,17 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8633,12 +8773,12 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8791,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8661,7 +8801,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8699,12 +8839,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8718,7 +8858,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8743,7 +8883,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8767,7 +8907,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8777,7 +8917,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8815,12 +8955,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8834,7 +8974,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8883,22 +9023,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8936,7 +9076,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8950,7 +9090,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8980,17 +9120,13 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9003,22 +9139,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9051,12 +9187,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9070,7 +9206,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9095,7 +9231,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9119,7 +9255,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9129,7 +9265,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9139,40 +9275,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9186,7 +9326,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9196,17 +9336,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9216,13 +9356,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9379,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9245,7 +9389,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9255,40 +9399,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9302,7 +9450,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9312,17 +9460,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9332,13 +9480,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9351,60 +9503,64 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9418,7 +9574,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9428,17 +9584,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9448,13 +9604,17 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9467,60 +9627,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9534,7 +9698,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9544,17 +9708,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9564,13 +9728,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9751,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9593,7 +9761,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9603,40 +9771,44 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9650,41 +9822,2641 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W78" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X78" s="2" t="inlineStr">
+      <c r="X92" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y78" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z78" s="2" t="inlineStr">
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
+      <c r="AA92" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB78" s="2" t="inlineStr">
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC78" s="2" t="inlineStr"/>
-      <c r="AD78" s="2" t="inlineStr">
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-27-operations.xlsx
+++ b/data/export/2026-10-27-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD298"/>
+  <dimension ref="A1:AD299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9380,12 +9380,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10673,19 +10673,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -10787,32 +10787,36 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10820,7 +10824,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10844,17 +10848,17 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10864,12 +10868,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
@@ -10907,32 +10911,36 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -10940,7 +10948,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10964,17 +10972,17 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10984,12 +10992,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11027,32 +11035,36 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11060,7 +11072,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11084,17 +11096,17 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -11104,12 +11116,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
@@ -11147,32 +11159,36 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11180,7 +11196,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11204,17 +11220,17 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -11224,12 +11240,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11300,7 +11316,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11349,12 +11365,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -11420,7 +11436,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11464,12 +11480,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11544,7 +11560,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11598,7 +11614,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11738,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11862,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12184,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12222,7 +12238,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12362,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12486,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12610,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12680,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12718,7 +12734,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12804,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12832,17 +12848,17 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -13044,7 +13060,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13088,17 +13104,17 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13304,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13358,7 +13374,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13444,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13482,7 +13498,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13676,7 +13692,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13796,7 +13812,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13845,12 +13861,12 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -13920,7 +13936,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13974,7 +13990,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14060,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14088,17 +14104,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14184,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14222,7 +14238,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14308,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14346,7 +14362,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14486,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14556,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14584,17 +14600,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14804,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14842,7 +14858,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14982,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15052,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15090,7 +15106,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -15214,7 +15230,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15556,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15594,7 +15610,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -15718,7 +15734,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15842,7 +15858,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -15966,7 +15982,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -16036,7 +16052,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16090,7 +16106,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16176,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16204,17 +16220,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16300,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16328,17 +16344,17 @@
       </c>
       <c r="AB128" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16548,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16586,7 +16602,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16796,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16904,7 +16920,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16953,12 +16969,12 @@
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -17028,7 +17044,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17082,7 +17098,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -17152,7 +17168,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17206,7 +17222,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17292,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17330,7 +17346,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -17524,7 +17540,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17578,7 +17594,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -17826,7 +17842,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17950,7 +17966,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18090,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -18140,7 +18156,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18516,7 +18532,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18570,7 +18586,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -18764,7 +18780,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18818,7 +18834,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -18888,7 +18904,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18942,7 +18958,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19028,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19066,7 +19082,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -19314,7 +19330,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19578,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19702,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -19810,7 +19826,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -20004,7 +20020,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20048,17 +20064,17 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -20260,7 +20276,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20304,17 +20320,17 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -20380,7 +20396,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20500,7 +20516,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20544,17 +20560,17 @@
       </c>
       <c r="AB162" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC162" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -20624,7 +20640,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20668,17 +20684,17 @@
       </c>
       <c r="AB163" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC163" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20764,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20802,7 +20818,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -20872,7 +20888,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20996,7 +21012,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21050,7 +21066,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -21120,7 +21136,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21174,7 +21190,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21260,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21298,7 +21314,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21384,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21422,7 +21438,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -21492,7 +21508,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21546,7 +21562,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -21670,7 +21686,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -21794,7 +21810,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -21918,7 +21934,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22042,7 +22058,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -22166,7 +22182,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22430,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22577,24 +22593,24 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O179" s="2" t="inlineStr">
@@ -22604,7 +22620,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22653,12 +22669,12 @@
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -22713,12 +22729,12 @@
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O180" s="2" t="inlineStr">
@@ -22728,7 +22744,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22782,7 +22798,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -22848,7 +22864,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22902,7 +22918,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22935,32 +22951,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22968,7 +22988,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22992,17 +23012,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -23012,17 +23032,17 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -23055,32 +23075,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23088,7 +23112,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23112,17 +23136,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23132,17 +23156,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23204,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -23208,7 +23232,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23278,7 +23302,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23311,32 +23335,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23344,7 +23372,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23368,17 +23396,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23388,17 +23416,17 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -23431,32 +23459,36 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N186" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23464,7 +23496,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23488,17 +23520,17 @@
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA186" s="2" t="inlineStr">
@@ -23508,17 +23540,17 @@
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23616,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23638,7 +23670,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -23671,12 +23703,12 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq46，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -23704,7 +23736,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23712,10 +23744,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R188" s="2" t="inlineStr"/>
-      <c r="S188" s="2" t="inlineStr"/>
-      <c r="T188" s="2" t="inlineStr"/>
-      <c r="U188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V188" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -23758,7 +23806,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -23824,7 +23872,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23944,7 +23992,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23998,7 +24046,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24112,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24118,7 +24166,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24232,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24238,7 +24286,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -24304,7 +24352,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24358,7 +24406,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -24424,7 +24472,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24473,12 +24521,12 @@
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -24548,7 +24596,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24592,17 +24640,17 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -24722,7 +24770,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -24842,7 +24890,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -25032,7 +25080,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25076,12 +25124,12 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
@@ -25152,7 +25200,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25201,12 +25249,12 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -25516,7 +25564,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25560,17 +25608,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -25640,7 +25688,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25684,17 +25732,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -26066,7 +26114,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26186,7 +26234,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26358,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -26380,7 +26428,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26419,17 +26467,17 @@
       </c>
       <c r="AA210" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB210" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB210" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
@@ -26504,7 +26552,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26548,17 +26596,17 @@
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26682,7 +26730,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26802,7 +26850,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26996,7 +27044,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27045,12 +27093,12 @@
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -27174,7 +27222,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27244,7 +27292,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27288,12 +27336,12 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
@@ -27740,7 +27788,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27784,17 +27832,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -27864,7 +27912,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27908,17 +27956,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28290,7 +28338,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -28414,7 +28462,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -28484,7 +28532,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28523,17 +28571,17 @@
       </c>
       <c r="AA227" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB227" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB227" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
@@ -28662,7 +28710,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28958,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -28976,7 +29024,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29037,12 +29085,12 @@
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -29232,7 +29280,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29288,17 +29336,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29842,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -29918,7 +29966,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30042,7 +30090,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30290,7 +30338,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -30902,7 +30950,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -31026,7 +31074,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -31150,7 +31198,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -31398,7 +31446,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31468,7 +31516,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31512,17 +31560,17 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32014,7 +32062,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -32208,7 +32256,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32252,12 +32300,12 @@
       </c>
       <c r="AB257" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC257" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD257" s="2" t="inlineStr">
@@ -32386,7 +32434,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -32456,7 +32504,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32500,17 +32548,17 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32634,7 +32682,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32758,7 +32806,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32828,7 +32876,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32877,12 +32925,12 @@
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32952,7 +33000,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32991,17 +33039,17 @@
       </c>
       <c r="AA263" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB263" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB263" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -33130,7 +33178,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33196,7 +33244,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33240,17 +33288,17 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -33498,7 +33546,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -33688,7 +33736,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33732,17 +33780,17 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34278,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -34296,7 +34344,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34340,12 +34388,12 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
@@ -34474,7 +34522,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -34540,7 +34588,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34584,17 +34632,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34714,7 +34762,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34838,7 +34886,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34908,7 +34956,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34957,12 +35005,12 @@
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35032,7 +35080,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35071,17 +35119,17 @@
       </c>
       <c r="AA280" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB280" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB280" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
@@ -35210,7 +35258,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35396,7 +35444,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35440,17 +35488,17 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -35690,7 +35738,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -35756,7 +35804,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35800,17 +35848,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36058,7 +36106,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -36302,7 +36350,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36335,36 +36383,32 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr"/>
       <c r="M291" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N291" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N291" s="2" t="inlineStr"/>
       <c r="O291" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -36372,7 +36416,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36396,17 +36440,17 @@
       </c>
       <c r="X291" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y291" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z291" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA291" s="2" t="inlineStr">
@@ -36416,12 +36460,12 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
@@ -36469,12 +36513,12 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K292" s="2" t="inlineStr"/>
@@ -36496,7 +36540,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36545,12 +36589,12 @@
       </c>
       <c r="AC292" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -36583,32 +36627,36 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr"/>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N293" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O293" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -36616,7 +36664,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36640,17 +36688,17 @@
       </c>
       <c r="X293" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z293" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA293" s="2" t="inlineStr">
@@ -36660,17 +36708,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36703,32 +36751,36 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr"/>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N294" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O294" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -36736,7 +36788,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36760,32 +36812,32 @@
       </c>
       <c r="X294" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z294" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA294" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB294" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB294" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
@@ -36823,32 +36875,36 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr"/>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N295" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O295" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -36856,7 +36912,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36880,17 +36936,17 @@
       </c>
       <c r="X295" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y295" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z295" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA295" s="2" t="inlineStr">
@@ -36900,17 +36956,17 @@
       </c>
       <c r="AB295" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC295" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -36943,32 +36999,36 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N296" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O296" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -36976,7 +37036,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37000,17 +37060,17 @@
       </c>
       <c r="X296" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA296" s="2" t="inlineStr">
@@ -37020,17 +37080,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37053,7 +37113,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
@@ -37096,7 +37156,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37110,7 +37170,7 @@
       <c r="U297" s="2" t="inlineStr"/>
       <c r="V297" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="W297" s="2" t="inlineStr">
@@ -37140,12 +37200,12 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
@@ -37216,7 +37276,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37260,17 +37320,137 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr"/>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr"/>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N299" s="2" t="inlineStr"/>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr"/>
+      <c r="S299" s="2" t="inlineStr"/>
+      <c r="T299" s="2" t="inlineStr"/>
+      <c r="U299" s="2" t="inlineStr"/>
+      <c r="V299" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="W299" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X299" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y299" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z299" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA299" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB299" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC299" s="2" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="AD299" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-operations.xlsx
+++ b/data/export/2026-10-27-operations.xlsx
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1588,17 +1588,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4676,17 +4676,17 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5668,17 +5668,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9256,17 +9256,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10744,17 +10744,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11169,24 +11169,24 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11283,32 +11283,36 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11316,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11340,17 +11344,17 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -11360,17 +11364,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11440,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11560,7 +11564,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11604,12 +11608,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11862,7 +11866,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11990,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12188,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12238,7 +12242,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12614,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12684,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -13114,7 +13118,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13242,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13378,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13626,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13696,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13736,12 +13740,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
@@ -13812,7 +13816,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13866,7 +13870,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13940,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13980,17 +13984,17 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14118,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14242,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14614,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14808,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -15052,7 +15056,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15096,12 +15100,12 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
@@ -15230,7 +15234,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15358,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -15556,7 +15560,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15610,7 +15614,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -15982,7 +15986,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16056,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16354,7 +16358,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16482,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -16726,7 +16730,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -16796,7 +16800,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16840,12 +16844,12 @@
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
@@ -16920,7 +16924,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16974,7 +16978,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17098,7 +17102,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17172,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17212,17 +17216,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -17540,7 +17544,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17718,7 +17722,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17846,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18094,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18466,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -18586,7 +18590,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -18710,7 +18714,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -18958,7 +18962,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -19028,7 +19032,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19072,17 +19076,17 @@
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19458,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20334,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20574,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20698,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -20818,7 +20822,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20888,7 +20892,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20932,12 +20936,12 @@
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC165" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AD165" s="2" t="inlineStr">
@@ -21136,7 +21140,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21180,12 +21184,12 @@
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
@@ -21260,7 +21264,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21384,7 +21388,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21438,7 +21442,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21512,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21686,7 +21690,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -21810,7 +21814,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -22306,7 +22310,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -22620,7 +22624,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22674,7 +22678,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -22798,7 +22802,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -23042,7 +23046,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23430,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -23550,7 +23554,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -23670,7 +23674,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23708,7 +23712,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq46，推进18站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -23736,7 +23740,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23839,32 +23843,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23872,7 +23880,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23896,17 +23904,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23916,12 +23924,12 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
@@ -23959,32 +23967,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23992,7 +24004,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24016,17 +24028,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -24036,12 +24048,12 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
@@ -24079,32 +24091,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -24112,7 +24128,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24136,17 +24152,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24156,17 +24172,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -24232,7 +24248,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24286,7 +24302,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -24352,7 +24368,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24472,7 +24488,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24526,7 +24542,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -24596,7 +24612,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24645,12 +24661,12 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -25080,7 +25096,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25494,7 +25510,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -25564,7 +25580,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25608,17 +25624,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26114,7 +26130,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26428,7 +26444,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26552,7 +26568,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26601,12 +26617,12 @@
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27292,7 +27308,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27718,7 +27734,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27912,7 +27928,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27956,17 +27972,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28462,7 +28478,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28532,7 +28548,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -29470,7 +29486,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29966,7 +29982,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30582,7 +30598,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31074,7 +31090,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31516,7 +31532,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31565,12 +31581,12 @@
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -31942,7 +31958,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32256,7 +32272,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32504,7 +32520,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32548,17 +32564,17 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32806,7 +32822,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33000,7 +33016,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33736,7 +33752,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33785,12 +33801,12 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34038,7 +34054,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34344,7 +34360,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34588,7 +34604,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34632,17 +34648,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34886,7 +34902,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35080,7 +35096,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35804,7 +35820,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35853,12 +35869,12 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36416,7 +36432,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36664,7 +36680,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36708,17 +36724,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36788,7 +36804,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -37009,24 +37025,24 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N296" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O296" s="2" t="inlineStr">
@@ -37036,7 +37052,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37085,12 +37101,12 @@
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37156,7 +37172,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37243,32 +37259,36 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr"/>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N298" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O298" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -37276,7 +37296,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37300,17 +37320,17 @@
       </c>
       <c r="X298" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA298" s="2" t="inlineStr">
@@ -37320,17 +37340,17 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37396,7 +37416,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
